--- a/Result_Merged.xlsx
+++ b/Result_Merged.xlsx
@@ -12,8 +12,32 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="E4" authorId="0">
+      <text>
+        <r>
+          <t>No unambiguous assent file for this participant.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M4" authorId="0">
+      <text>
+        <r>
+          <t>Birthdate needs a manual fix: Could not recognise "not recorded" as a date. Left exactly as submitted.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="102">
   <si>
     <t>participant_sequence</t>
   </si>
@@ -105,10 +129,19 @@
     <t>Assent URL</t>
   </si>
   <si>
+    <t>Auto-fixed</t>
+  </si>
+  <si>
+    <t>Whitespace tidied: Leading, trailing or repeated spaces removed. | Whitespace tidied: Leading, trailing or repeated spaces removed. | Birthdate reformatted to YYYY/MM: Reformatted to YYYY/MM.</t>
+  </si>
+  <si>
     <t>ABRAHAM OTIENO</t>
   </si>
   <si>
-    <t>https://www.dropbox.com/scl/fi/q/F?rlkey=k&amp;dl=0</t>
+    <t>https://www.dropbox.com/scl/fi/n33/F?rlkey=k&amp;dl=0</t>
+  </si>
+  <si>
+    <t>a@x</t>
   </si>
   <si>
     <t>Neutral</t>
@@ -123,6 +156,57 @@
     <t>Glasses</t>
   </si>
   <si>
+    <t>Deep Brown</t>
+  </si>
+  <si>
+    <t>Kenya</t>
+  </si>
+  <si>
+    <t>https://www.dropbox.com/scl/fi/n26/F?rlkey=k&amp;dl=0</t>
+  </si>
+  <si>
+    <t>https://www.dropbox.com/scl/fi/n25/F?rlkey=k&amp;dl=0</t>
+  </si>
+  <si>
+    <t>Birthdate reformatted to YYYY/MM: Reformatted to YYYY/MM.</t>
+  </si>
+  <si>
+    <t>Non-Neutral</t>
+  </si>
+  <si>
+    <t>Smiling</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Birthdate needs a manual fix: Could not recognise "not recorded" as a date. Left exactly as submitted. | No unambiguous assent file for this participant.</t>
+  </si>
+  <si>
+    <t>ASNET KALAI</t>
+  </si>
+  <si>
+    <t>https://www.dropbox.com/scl/fi/n29/F?rlkey=k&amp;dl=0</t>
+  </si>
+  <si>
+    <t>b@x</t>
+  </si>
+  <si>
+    <t>Angry</t>
+  </si>
+  <si>
+    <t>not recorded</t>
+  </si>
+  <si>
+    <t>Outdoor</t>
+  </si>
+  <si>
+    <t>N/A-none apply</t>
+  </si>
+  <si>
+    <t>https://www.dropbox.com/scl/fi/n23/F?rlkey=k&amp;dl=0</t>
+  </si>
+  <si>
     <t>Severity</t>
   </si>
   <si>
@@ -153,7 +237,22 @@
     <t>FIXED</t>
   </si>
   <si>
-    <t>A_metadata.xlsx</t>
+    <t>meta.xlsx</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Whitespace tidied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ABRAHAM   OTIENO </t>
+  </si>
+  <si>
+    <t>Leading, trailing or repeated spaces removed.</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>M</t>
@@ -168,7 +267,13 @@
     <t>Reformatted to YYYY/MM.</t>
   </si>
   <si>
-    <t>B_metadata.xlsx</t>
+    <t>REVIEW</t>
+  </si>
+  <si>
+    <t>Birthdate needs a manual fix</t>
+  </si>
+  <si>
+    <t>Could not recognise "not recorded" as a date. Left exactly as submitted.</t>
   </si>
   <si>
     <t xml:space="preserve">Facial Features </t>
@@ -260,7 +365,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,6 +375,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -285,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -295,6 +405,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -636,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -761,79 +873,169 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="W2" t="s">
+        <v>39</v>
       </c>
       <c r="Z2" s="4">
         <v>46233.375</v>
       </c>
+      <c r="AA2" t="s">
+        <v>40</v>
+      </c>
       <c r="AC2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AD2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>44</v>
+      </c>
+      <c r="K3" t="s">
+        <v>45</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R3" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="W3" t="s">
+        <v>39</v>
       </c>
       <c r="Z3" s="4">
         <v>46233.375</v>
       </c>
+      <c r="AA3" t="s">
+        <v>40</v>
+      </c>
       <c r="AC3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AD3" t="s">
-        <v>31</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>53</v>
+      </c>
+      <c r="V4" t="s">
+        <v>54</v>
+      </c>
+      <c r="W4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>46233.375</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AD1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -846,91 +1048,178 @@
     <col min="9" max="9" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>44</v>
+    <row r="1" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" t="s">
-        <v>50</v>
+      <c r="F5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -948,101 +1237,101 @@
     <col min="1" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
